--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487828_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487828_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>W. CABRAL BUERIBERI</t>
+          <t>J. CEBOLLA HERRERA</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>8.032999999999999</v>
+        <v>8.2927</v>
       </c>
       <c r="E2" t="n">
-        <v>4.1942</v>
+        <v>5.5715</v>
       </c>
       <c r="F2" t="n">
-        <v>3.8389</v>
+        <v>2.7212</v>
       </c>
       <c r="G2" t="n">
-        <v>0.5723</v>
+        <v>4.3086</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.0939</v>
+        <v>1.0535</v>
       </c>
       <c r="I2" t="n">
-        <v>0.6662</v>
+        <v>3.2551</v>
       </c>
       <c r="J2" t="n">
-        <v>-1.1625</v>
+        <v>2.3125</v>
       </c>
       <c r="K2" t="n">
-        <v>-1.1837</v>
+        <v>0.0576</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0212</v>
+        <v>2.2549</v>
       </c>
       <c r="M2" t="n">
-        <v>1.7348</v>
+        <v>1.9961</v>
       </c>
       <c r="N2" t="n">
-        <v>1.0898</v>
+        <v>0.996</v>
       </c>
       <c r="O2" t="n">
-        <v>0.645</v>
+        <v>1.0001</v>
       </c>
       <c r="P2" t="n">
-        <v>2.0812</v>
+        <v>1.6649</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>2.0812</v>
+        <v>1.6649</v>
       </c>
       <c r="S2" t="n">
-        <v>1.8769</v>
+        <v>1.1517</v>
       </c>
       <c r="T2" t="n">
-        <v>1.8541</v>
+        <v>0.9239000000000001</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0229</v>
+        <v>0.2277</v>
       </c>
       <c r="V2" t="n">
-        <v>3.5026</v>
+        <v>1.1675</v>
       </c>
       <c r="W2" t="n">
-        <v>3.5026</v>
+        <v>2.3351</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>-1.1675</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>J. CEBOLLA HERRERA</t>
+          <t>W. CABRAL BUERIBERI</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>7.8496</v>
+        <v>7.7364</v>
       </c>
       <c r="E3" t="n">
-        <v>5.3339</v>
+        <v>3.5746</v>
       </c>
       <c r="F3" t="n">
-        <v>2.5157</v>
+        <v>4.1618</v>
       </c>
       <c r="G3" t="n">
-        <v>4.3086</v>
+        <v>0.5723</v>
       </c>
       <c r="H3" t="n">
-        <v>1.0535</v>
+        <v>-0.0939</v>
       </c>
       <c r="I3" t="n">
-        <v>3.2551</v>
+        <v>0.6662</v>
       </c>
       <c r="J3" t="n">
-        <v>2.3125</v>
+        <v>-1.1625</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0576</v>
+        <v>-1.1837</v>
       </c>
       <c r="L3" t="n">
-        <v>2.2549</v>
+        <v>0.0212</v>
       </c>
       <c r="M3" t="n">
-        <v>1.9961</v>
+        <v>1.7348</v>
       </c>
       <c r="N3" t="n">
-        <v>0.996</v>
+        <v>1.0898</v>
       </c>
       <c r="O3" t="n">
-        <v>1.0001</v>
+        <v>0.645</v>
       </c>
       <c r="P3" t="n">
-        <v>1.6649</v>
+        <v>2.0812</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.6649</v>
+        <v>2.0812</v>
       </c>
       <c r="S3" t="n">
-        <v>0.7085</v>
+        <v>1.5803</v>
       </c>
       <c r="T3" t="n">
-        <v>0.6863</v>
+        <v>1.2345</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0222</v>
+        <v>0.3458</v>
       </c>
       <c r="V3" t="n">
-        <v>1.1675</v>
+        <v>3.5026</v>
       </c>
       <c r="W3" t="n">
-        <v>2.3351</v>
+        <v>3.5026</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.1675</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.4552</v>
+        <v>4.4793</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0157</v>
+        <v>0.5095</v>
       </c>
       <c r="F4" t="n">
-        <v>4.4395</v>
+        <v>3.9698</v>
       </c>
       <c r="G4" t="n">
         <v>2.982</v>
@@ -766,13 +766,13 @@
         <v>2.0812</v>
       </c>
       <c r="S4" t="n">
-        <v>1.4732</v>
+        <v>1.4973</v>
       </c>
       <c r="T4" t="n">
-        <v>0.6211</v>
+        <v>1.1149</v>
       </c>
       <c r="U4" t="n">
-        <v>0.8521</v>
+        <v>0.3824</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.6178</v>
+        <v>4.1094</v>
       </c>
       <c r="E5" t="n">
-        <v>0.2513</v>
+        <v>0.5961</v>
       </c>
       <c r="F5" t="n">
-        <v>3.3665</v>
+        <v>3.5133</v>
       </c>
       <c r="G5" t="n">
         <v>3.3118</v>
@@ -844,13 +844,13 @@
         <v>1.6649</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.3184</v>
+        <v>0.1732</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.6524</v>
+        <v>-0.3076</v>
       </c>
       <c r="U5" t="n">
-        <v>0.3341</v>
+        <v>0.4809</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>M. JANKOVIC</t>
+          <t>S. CECILIA PEREZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,64 +877,64 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>3.2227</v>
+        <v>4.106</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.424</v>
+        <v>2.1931</v>
       </c>
       <c r="F6" t="n">
-        <v>3.6467</v>
+        <v>1.913</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.5987</v>
+        <v>2.6717</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.2094</v>
+        <v>0.2837</v>
       </c>
       <c r="I6" t="n">
-        <v>0.6107</v>
+        <v>2.388</v>
       </c>
       <c r="J6" t="n">
-        <v>-1.0884</v>
+        <v>2.7617</v>
       </c>
       <c r="K6" t="n">
-        <v>-1.1969</v>
+        <v>0.341</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1086</v>
+        <v>2.4207</v>
       </c>
       <c r="M6" t="n">
-        <v>0.4897</v>
+        <v>-0.08989999999999999</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.0124</v>
+        <v>-0.0573</v>
       </c>
       <c r="O6" t="n">
-        <v>0.5021</v>
+        <v>-0.0326</v>
       </c>
       <c r="P6" t="n">
-        <v>1.0406</v>
+        <v>0.8325</v>
       </c>
       <c r="Q6" t="n">
-        <v>-2.0812</v>
+        <v>-1.0406</v>
       </c>
       <c r="R6" t="n">
-        <v>3.1218</v>
+        <v>1.8731</v>
       </c>
       <c r="S6" t="n">
-        <v>2.5509</v>
+        <v>0.6018</v>
       </c>
       <c r="T6" t="n">
-        <v>2.5156</v>
+        <v>0.472</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0353</v>
+        <v>0.1299</v>
       </c>
       <c r="V6" t="n">
-        <v>0.23</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>0.23</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>S. CECILIA PEREZ</t>
+          <t>G. CLARKE</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,58 +955,58 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>2.9509</v>
+        <v>3.8818</v>
       </c>
       <c r="E7" t="n">
-        <v>1.4196</v>
+        <v>0.1735</v>
       </c>
       <c r="F7" t="n">
-        <v>1.5313</v>
+        <v>3.7083</v>
       </c>
       <c r="G7" t="n">
-        <v>2.6717</v>
+        <v>2.4343</v>
       </c>
       <c r="H7" t="n">
-        <v>0.2837</v>
+        <v>1.533</v>
       </c>
       <c r="I7" t="n">
-        <v>2.388</v>
+        <v>0.9013</v>
       </c>
       <c r="J7" t="n">
-        <v>2.7617</v>
+        <v>2.0018</v>
       </c>
       <c r="K7" t="n">
-        <v>0.341</v>
+        <v>1.3535</v>
       </c>
       <c r="L7" t="n">
-        <v>2.4207</v>
+        <v>0.6482</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.08989999999999999</v>
+        <v>0.4325</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.0573</v>
+        <v>0.1794</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.0326</v>
+        <v>0.2531</v>
       </c>
       <c r="P7" t="n">
-        <v>0.8325</v>
+        <v>0.4162</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.0406</v>
+        <v>-2.0812</v>
       </c>
       <c r="R7" t="n">
-        <v>1.8731</v>
+        <v>2.4974</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.5532</v>
+        <v>1.0313</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.3014</v>
+        <v>0.2529</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.2518</v>
+        <v>0.7784</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. LATORRE SANCHEZ</t>
+          <t>R. SANTOS JIMENEZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>2.8746</v>
+        <v>3.0624</v>
       </c>
       <c r="E8" t="n">
-        <v>0.7873</v>
+        <v>-0.0374</v>
       </c>
       <c r="F8" t="n">
-        <v>2.0874</v>
+        <v>3.0998</v>
       </c>
       <c r="G8" t="n">
-        <v>0.8843</v>
+        <v>2.1149</v>
       </c>
       <c r="H8" t="n">
-        <v>0.5479000000000001</v>
+        <v>-0.8977000000000001</v>
       </c>
       <c r="I8" t="n">
-        <v>0.3364</v>
+        <v>3.0126</v>
       </c>
       <c r="J8" t="n">
-        <v>0.5701000000000001</v>
+        <v>2.2661</v>
       </c>
       <c r="K8" t="n">
-        <v>0.4133</v>
+        <v>-0.7423999999999999</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1568</v>
+        <v>3.0085</v>
       </c>
       <c r="M8" t="n">
-        <v>0.3142</v>
+        <v>-0.1512</v>
       </c>
       <c r="N8" t="n">
-        <v>0.1346</v>
+        <v>-0.1553</v>
       </c>
       <c r="O8" t="n">
-        <v>0.1796</v>
+        <v>0.0041</v>
       </c>
       <c r="P8" t="n">
-        <v>0.4162</v>
+        <v>-0.6244</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.0406</v>
+        <v>-3.1218</v>
       </c>
       <c r="R8" t="n">
-        <v>1.4568</v>
+        <v>2.4974</v>
       </c>
       <c r="S8" t="n">
-        <v>1.4503</v>
+        <v>1.5718</v>
       </c>
       <c r="T8" t="n">
-        <v>1.2578</v>
+        <v>0.8182</v>
       </c>
       <c r="U8" t="n">
-        <v>0.1925</v>
+        <v>0.7536</v>
       </c>
       <c r="V8" t="n">
-        <v>0.1238</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0.1238</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>R. SANTOS JIMENEZ</t>
+          <t>M. JANKOVIC</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,64 +1111,64 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>2.8593</v>
+        <v>2.3484</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.7689</v>
+        <v>-1.6213</v>
       </c>
       <c r="F9" t="n">
-        <v>3.6283</v>
+        <v>3.9697</v>
       </c>
       <c r="G9" t="n">
-        <v>2.1149</v>
+        <v>-0.5987</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.8977000000000001</v>
+        <v>-1.2094</v>
       </c>
       <c r="I9" t="n">
-        <v>3.0126</v>
+        <v>0.6107</v>
       </c>
       <c r="J9" t="n">
-        <v>2.2661</v>
+        <v>-1.0884</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.7423999999999999</v>
+        <v>-1.1969</v>
       </c>
       <c r="L9" t="n">
-        <v>3.0085</v>
+        <v>0.1086</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.1512</v>
+        <v>0.4897</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.1553</v>
+        <v>-0.0124</v>
       </c>
       <c r="O9" t="n">
-        <v>0.0041</v>
+        <v>0.5021</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.6244</v>
+        <v>1.0406</v>
       </c>
       <c r="Q9" t="n">
-        <v>-3.1218</v>
+        <v>-2.0812</v>
       </c>
       <c r="R9" t="n">
-        <v>2.4974</v>
+        <v>3.1218</v>
       </c>
       <c r="S9" t="n">
-        <v>1.3688</v>
+        <v>1.6765</v>
       </c>
       <c r="T9" t="n">
-        <v>0.0867</v>
+        <v>1.3183</v>
       </c>
       <c r="U9" t="n">
-        <v>1.2821</v>
+        <v>0.3582</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>0.23</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>0.23</v>
       </c>
       <c r="X9" t="n">
         <v>0</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>G. CLARKE</t>
+          <t>A. LATORRE SANCHEZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>2.8121</v>
+        <v>2.2219</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.8376</v>
+        <v>0.3401</v>
       </c>
       <c r="F10" t="n">
-        <v>3.6496</v>
+        <v>1.8819</v>
       </c>
       <c r="G10" t="n">
-        <v>2.4343</v>
+        <v>0.8843</v>
       </c>
       <c r="H10" t="n">
-        <v>1.533</v>
+        <v>0.5479000000000001</v>
       </c>
       <c r="I10" t="n">
-        <v>0.9013</v>
+        <v>0.3364</v>
       </c>
       <c r="J10" t="n">
-        <v>2.0018</v>
+        <v>0.5701000000000001</v>
       </c>
       <c r="K10" t="n">
-        <v>1.3535</v>
+        <v>0.4133</v>
       </c>
       <c r="L10" t="n">
-        <v>0.6482</v>
+        <v>0.1568</v>
       </c>
       <c r="M10" t="n">
-        <v>0.4325</v>
+        <v>0.3142</v>
       </c>
       <c r="N10" t="n">
-        <v>0.1794</v>
+        <v>0.1346</v>
       </c>
       <c r="O10" t="n">
-        <v>0.2531</v>
+        <v>0.1796</v>
       </c>
       <c r="P10" t="n">
         <v>0.4162</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.0812</v>
+        <v>-1.0406</v>
       </c>
       <c r="R10" t="n">
-        <v>2.4974</v>
+        <v>1.4568</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.0385</v>
+        <v>0.7976</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.7581</v>
+        <v>0.8106</v>
       </c>
       <c r="U10" t="n">
-        <v>0.7197</v>
+        <v>-0.013</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>0.1238</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>0.1238</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>1.3017</v>
+        <v>1.4616</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.2179</v>
+        <v>-2.0874</v>
       </c>
       <c r="F11" t="n">
-        <v>3.5196</v>
+        <v>3.549</v>
       </c>
       <c r="G11" t="n">
         <v>0.3438</v>
@@ -1312,13 +1312,13 @@
         <v>2.0812</v>
       </c>
       <c r="S11" t="n">
-        <v>1.5416</v>
+        <v>1.7015</v>
       </c>
       <c r="T11" t="n">
-        <v>0.6582</v>
+        <v>0.7887</v>
       </c>
       <c r="U11" t="n">
-        <v>0.8834</v>
+        <v>0.9127999999999999</v>
       </c>
       <c r="V11" t="n">
         <v>-0.5838</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>1.0098</v>
+        <v>1.3172</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.0174</v>
+        <v>-2.4164</v>
       </c>
       <c r="F12" t="n">
-        <v>4.0272</v>
+        <v>3.7336</v>
       </c>
       <c r="G12" t="n">
         <v>0.9165</v>
@@ -1390,13 +1390,13 @@
         <v>1.4568</v>
       </c>
       <c r="S12" t="n">
-        <v>0.7177</v>
+        <v>1.0251</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.09329999999999999</v>
+        <v>0.5077</v>
       </c>
       <c r="U12" t="n">
-        <v>0.8110000000000001</v>
+        <v>0.5174</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.0581</v>
+        <v>-0.4573</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.8449</v>
+        <v>-1.2735</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7868000000000001</v>
+        <v>0.8162</v>
       </c>
       <c r="G13" t="n">
         <v>-1.143</v>
@@ -1468,13 +1468,13 @@
         <v>0.4162</v>
       </c>
       <c r="S13" t="n">
-        <v>0.6687</v>
+        <v>0.2694</v>
       </c>
       <c r="T13" t="n">
-        <v>0.5839</v>
+        <v>0.1553</v>
       </c>
       <c r="U13" t="n">
-        <v>0.0848</v>
+        <v>0.1142</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>40.9286</v>
+        <v>42.5598</v>
       </c>
       <c r="E14" t="n">
-        <v>3.891299999999998</v>
+        <v>5.522399999999999</v>
       </c>
       <c r="F14" t="n">
-        <v>37.03749999999999</v>
+        <v>37.0376</v>
       </c>
       <c r="G14" t="n">
         <v>18.7985</v>
@@ -1534,10 +1534,10 @@
         <v>6.346500000000001</v>
       </c>
       <c r="O14" t="n">
-        <v>5.0211</v>
+        <v>5.021100000000001</v>
       </c>
       <c r="P14" t="n">
-        <v>6.2434</v>
+        <v>6.243399999999999</v>
       </c>
       <c r="Q14" t="n">
         <v>-16.6496</v>
@@ -1546,16 +1546,16 @@
         <v>22.8929</v>
       </c>
       <c r="S14" t="n">
-        <v>11.4465</v>
+        <v>13.0775</v>
       </c>
       <c r="T14" t="n">
-        <v>6.4585</v>
+        <v>8.089399999999999</v>
       </c>
       <c r="U14" t="n">
-        <v>4.9883</v>
+        <v>4.988300000000001</v>
       </c>
       <c r="V14" t="n">
-        <v>4.440099999999999</v>
+        <v>4.4401</v>
       </c>
       <c r="W14" t="n">
         <v>6.6515</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.3247</v>
+        <v>2.6001</v>
       </c>
       <c r="E15" t="n">
-        <v>1.017</v>
+        <v>1.1241</v>
       </c>
       <c r="F15" t="n">
-        <v>1.3077</v>
+        <v>1.476</v>
       </c>
       <c r="G15" t="n">
         <v>1.7258</v>
@@ -1624,13 +1624,13 @@
         <v>2.0812</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.2741</v>
+        <v>-0.9987</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.8110000000000001</v>
+        <v>-0.7038</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.4631</v>
+        <v>-0.2948</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.1919</v>
+        <v>1.8094</v>
       </c>
       <c r="E16" t="n">
-        <v>1.6089</v>
+        <v>1.8232</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.4171</v>
+        <v>-0.0139</v>
       </c>
       <c r="G16" t="n">
         <v>1.1722</v>
@@ -1702,13 +1702,13 @@
         <v>2.0812</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.5214</v>
+        <v>-0.9039</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.6277</v>
+        <v>-0.4133</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.8938</v>
+        <v>-0.4906</v>
       </c>
       <c r="V16" t="n">
         <v>-0.1238</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.9205</v>
+        <v>-0.5085</v>
       </c>
       <c r="E17" t="n">
-        <v>-2.1465</v>
+        <v>-1.9322</v>
       </c>
       <c r="F17" t="n">
-        <v>1.226</v>
+        <v>1.4237</v>
       </c>
       <c r="G17" t="n">
         <v>-0.6165</v>
@@ -1780,13 +1780,13 @@
         <v>0.6244</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.7202</v>
+        <v>-0.3083</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.5872000000000001</v>
+        <v>-0.3729</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.133</v>
+        <v>0.0646</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-2.3014</v>
+        <v>-2.1062</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.3024</v>
+        <v>-1.1953</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.999</v>
+        <v>-0.9109</v>
       </c>
       <c r="G18" t="n">
         <v>-1.6706</v>
@@ -1858,13 +1858,13 @@
         <v>0.6244</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.0471</v>
+        <v>-0.8519</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.4567</v>
+        <v>-0.3495</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.5904</v>
+        <v>-0.5023</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.5553</v>
+        <v>-2.3307</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.3106</v>
+        <v>-2.2034</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.2447</v>
+        <v>-0.1272</v>
       </c>
       <c r="G19" t="n">
         <v>-1.2015</v>
@@ -1936,13 +1936,13 @@
         <v>0.6244</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.9375</v>
+        <v>-0.7129</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.5748</v>
+        <v>-0.4676</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.3627</v>
+        <v>-0.2453</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.8266</v>
+        <v>-4.2479</v>
       </c>
       <c r="E20" t="n">
-        <v>-3.6224</v>
+        <v>-3.9439</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.2042</v>
+        <v>-0.3041</v>
       </c>
       <c r="G20" t="n">
         <v>-0.7068</v>
@@ -2014,13 +2014,13 @@
         <v>2.0812</v>
       </c>
       <c r="S20" t="n">
-        <v>0.2101</v>
+        <v>-0.2112</v>
       </c>
       <c r="T20" t="n">
-        <v>0.3072</v>
+        <v>-0.0142</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.09710000000000001</v>
+        <v>-0.197</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A. LOPES MARQUES</t>
+          <t>J. SANTA BARBARA CARCELEN</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-4.1971</v>
+        <v>-4.5135</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.8363</v>
+        <v>-3.1776</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.3609</v>
+        <v>-1.336</v>
       </c>
       <c r="G21" t="n">
-        <v>-2.9159</v>
+        <v>-2.8571</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.853</v>
+        <v>-1.6121</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.063</v>
+        <v>-1.245</v>
       </c>
       <c r="J21" t="n">
-        <v>-3.4751</v>
+        <v>-2.7999</v>
       </c>
       <c r="K21" t="n">
-        <v>-2.7999</v>
+        <v>-2.0856</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.6752</v>
+        <v>-0.7144</v>
       </c>
       <c r="M21" t="n">
-        <v>0.5592</v>
+        <v>-0.0572</v>
       </c>
       <c r="N21" t="n">
-        <v>0.947</v>
+        <v>0.4735</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.3878</v>
+        <v>-0.5306999999999999</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.8325</v>
+        <v>1.0406</v>
       </c>
       <c r="Q21" t="n">
-        <v>-2.0812</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.2487</v>
+        <v>1.0406</v>
       </c>
       <c r="S21" t="n">
-        <v>0.135</v>
+        <v>-0.3619</v>
       </c>
       <c r="T21" t="n">
-        <v>0.5525</v>
+        <v>-0.3776</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.4175</v>
+        <v>0.0157</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.5838</v>
+        <v>-2.3351</v>
       </c>
       <c r="W21" t="n">
-        <v>1.1675</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.7513</v>
+        <v>-2.3351</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>J. SANTA BARBARA CARCELEN</t>
+          <t>A. LOPES MARQUES</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.9319</v>
+        <v>-4.7726</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.2847</v>
+        <v>-4.6935</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.6471</v>
+        <v>-0.0791</v>
       </c>
       <c r="G22" t="n">
-        <v>-2.8571</v>
+        <v>-2.9159</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.6121</v>
+        <v>-1.853</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.245</v>
+        <v>-1.063</v>
       </c>
       <c r="J22" t="n">
+        <v>-3.4751</v>
+      </c>
+      <c r="K22" t="n">
         <v>-2.7999</v>
       </c>
-      <c r="K22" t="n">
-        <v>-2.0856</v>
-      </c>
       <c r="L22" t="n">
-        <v>-0.7144</v>
+        <v>-0.6752</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.0572</v>
+        <v>0.5592</v>
       </c>
       <c r="N22" t="n">
-        <v>0.4735</v>
+        <v>0.947</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.5306999999999999</v>
+        <v>-0.3878</v>
       </c>
       <c r="P22" t="n">
-        <v>1.0406</v>
+        <v>-0.8325</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>-2.0812</v>
       </c>
       <c r="R22" t="n">
-        <v>1.0406</v>
+        <v>1.2487</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.7803</v>
+        <v>-0.4404</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.4848</v>
+        <v>-0.3047</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.2955</v>
+        <v>-0.1357</v>
       </c>
       <c r="V22" t="n">
-        <v>-2.3351</v>
+        <v>-0.5838</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.1675</v>
       </c>
       <c r="X22" t="n">
-        <v>-2.3351</v>
+        <v>-1.7513</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-5.8413</v>
+        <v>-5.1611</v>
       </c>
       <c r="E23" t="n">
-        <v>-5.5905</v>
+        <v>-5.3762</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.2507</v>
+        <v>0.2151</v>
       </c>
       <c r="G23" t="n">
         <v>-3.1148</v>
@@ -2248,13 +2248,13 @@
         <v>1.2487</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.894</v>
+        <v>-1.2138</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.9539</v>
+        <v>-0.7396</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.9401</v>
+        <v>-0.4743</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-5.8483</v>
+        <v>-5.2499</v>
       </c>
       <c r="E24" t="n">
-        <v>-4.4318</v>
+        <v>-4.3246</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.4165</v>
+        <v>-0.9253</v>
       </c>
       <c r="G24" t="n">
         <v>-4.0499</v>
@@ -2326,13 +2326,13 @@
         <v>1.8731</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.1522</v>
+        <v>-0.5537</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.4195</v>
+        <v>-0.3124</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.7326</v>
+        <v>-0.2414</v>
       </c>
       <c r="V24" t="n">
         <v>-0.23</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-6.809</v>
+        <v>-5.8241</v>
       </c>
       <c r="E25" t="n">
-        <v>-6.4057</v>
+        <v>-6.0843</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.4033</v>
+        <v>0.2602</v>
       </c>
       <c r="G25" t="n">
         <v>-2.493</v>
@@ -2404,13 +2404,13 @@
         <v>1.2487</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.0673</v>
+        <v>-0.0824</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.3543</v>
+        <v>-0.0328</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.7131</v>
+        <v>-0.0496</v>
       </c>
       <c r="V25" t="n">
         <v>-1.1675</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-7.2139</v>
+        <v>-7.0519</v>
       </c>
       <c r="E26" t="n">
-        <v>-6.7324</v>
+        <v>-7.0539</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.4814</v>
+        <v>0.002</v>
       </c>
       <c r="G26" t="n">
         <v>-2.0703</v>
@@ -2482,13 +2482,13 @@
         <v>1.8731</v>
       </c>
       <c r="S26" t="n">
-        <v>-1.3974</v>
+        <v>-1.2355</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.5780999999999999</v>
+        <v>-0.8996</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.8193</v>
+        <v>-0.3359</v>
       </c>
       <c r="V26" t="n">
         <v>0</v>
@@ -2515,13 +2515,13 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-40.9287</v>
+        <v>-37.3569</v>
       </c>
       <c r="E27" t="n">
-        <v>-37.0374</v>
+        <v>-37.0376</v>
       </c>
       <c r="F27" t="n">
-        <v>-3.8912</v>
+        <v>-0.3195000000000001</v>
       </c>
       <c r="G27" t="n">
         <v>-18.7984</v>
@@ -2560,13 +2560,13 @@
         <v>16.6497</v>
       </c>
       <c r="S27" t="n">
-        <v>-11.4464</v>
+        <v>-7.8746</v>
       </c>
       <c r="T27" t="n">
-        <v>-4.988300000000001</v>
+        <v>-4.988</v>
       </c>
       <c r="U27" t="n">
-        <v>-6.4582</v>
+        <v>-2.8866</v>
       </c>
       <c r="V27" t="n">
         <v>-4.440200000000001</v>
